--- a/healthcare_forms/013_skin_treatment_feedback_survey--healthcare_forms.xlsx
+++ b/healthcare_forms/013_skin_treatment_feedback_survey--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>treatment_outcome</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What was the outcome of your skin treatment?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Select one</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>overall_experience</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Rate your overall experience</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>satisfaction</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How satisfied are you with the service?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,12 +601,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>treatment_issues</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Were there any issues with your treatment?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +624,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>feedback_treatment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Do you have any feedback about your treatment?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +647,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>improvement_service</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>How can we improve our service?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +670,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Additional comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +693,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>treatment_recommendation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Do you have any recommendations for us?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +716,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>How can we contact you?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +734,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>contact_method</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Contact method</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +762,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>follow_up_contact</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Would you like to be contacted for follow-up questions?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +780,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>follow_up_method</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>How would you like to be contacted?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +803,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>follow_up_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>When would you like to be contacted?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +826,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>follow_up_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What time would you like to be contacted?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +849,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>follow_up_note</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Additional information</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +877,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>follow_up_email</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Follow-up email address</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +900,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>follow_up_phone</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Follow-up phone number</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +923,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>follow_up_message</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Follow-up message</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,11 +949,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1131,12 +982,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +999,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1016,80 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>contact_method_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>contact_method_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>follow_up_method_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>follow_up_method_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>phone</t>
         </is>
       </c>
     </row>
